--- a/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语七年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语七年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D223"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -943,6 +943,16 @@
           <t>close to</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 接近于；在附近
@@ -956,6 +966,16 @@
           <t>go to school</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 到校上课；上学去；开始求学
@@ -969,6 +989,16 @@
           <t>good at</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 擅长；一清二楚；拿手的；精明的
@@ -982,6 +1012,16 @@
           <t>be good at</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 善于
@@ -995,6 +1035,16 @@
           <t>make friends with</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 跟…做朋友
@@ -1008,6 +1058,16 @@
           <t>all over</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 满
@@ -1022,6 +1082,16 @@
           <t>'d like to</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1032,6 +1102,16 @@
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>would like to</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1500,6 +1580,16 @@
           <t>junior high school</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. （美国）初级中学
@@ -1513,6 +1603,16 @@
           <t>on foot</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 步行；在进行中；徒步
@@ -1526,6 +1626,16 @@
           <t>take part in</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 参加；贡献
@@ -1539,6 +1649,16 @@
           <t>have a good time</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 过得愉快；很愉快
@@ -1550,6 +1670,16 @@
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>go to bed</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2209,6 +2339,16 @@
           <t>provide ... with ...</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 供给；供应
@@ -2220,6 +2360,16 @@
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>put ... into ...</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2705,6 +2855,16 @@
           <t>take a trip</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 旅行
@@ -2718,6 +2878,16 @@
           <t>go on a picnic</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 去野餐；去野炊；搞野餐</t>
@@ -2730,6 +2900,16 @@
           <t>make snowmen</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -2742,6 +2922,16 @@
           <t>fly kites</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 放风筝；放飞风筝；放级筝</t>
@@ -2754,6 +2944,16 @@
           <t>go swimming</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 去游泳
@@ -2765,6 +2965,16 @@
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>have a picnic</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -3316,6 +3526,16 @@
           <t>able to</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 可以；有能力；原来能够按时完成</t>
@@ -3328,6 +3548,16 @@
           <t>be able to</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 能够
@@ -3365,6 +3595,16 @@
           <t>so that</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">conj. 因此；以便
@@ -3378,6 +3618,16 @@
           <t>take photos</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 照相；拍照；拍照片</t>
@@ -3390,6 +3640,16 @@
           <t>as ... as</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 砷；用法；和……一样</t>
@@ -3400,6 +3660,16 @@
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>that is</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -3932,6 +4202,16 @@
           <t>travel guide</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 旅游指南；旅游与地理；旅行指南</t>
@@ -3944,6 +4224,16 @@
           <t>place of interest</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 名胜
@@ -3957,6 +4247,16 @@
           <t>in the centre of</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在……的中心；在……中部；在……中心</t>
@@ -3969,6 +4269,16 @@
           <t>light up</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 点灯；照亮；点香烟；变快活
@@ -3980,6 +4290,16 @@
       <c r="A165" s="2" t="inlineStr">
         <is>
           <t>in the north-west of</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -4463,6 +4783,16 @@
           <t>learn about</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 得知关于；学习关于
@@ -4476,6 +4806,16 @@
           <t>all the way</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 路上一直；老远；〈美〉(从…到…)逐一
@@ -4489,6 +4829,16 @@
           <t>of course</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 当然
@@ -4502,6 +4852,16 @@
           <t>remote control</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 遥控；遥控器
@@ -4513,6 +4873,16 @@
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>look up</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -5189,6 +5559,16 @@
           <t>bad for</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 有害于
@@ -5202,6 +5582,16 @@
           <t>be bad for</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 对…有害
@@ -5215,6 +5605,16 @@
           <t>interested in</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 感兴趣；尽力；关心；对…关注
@@ -5228,6 +5628,16 @@
           <t>be interested in</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 对…感兴趣
@@ -5239,6 +5649,16 @@
       <c r="A223" s="2" t="inlineStr">
         <is>
           <t>work of art</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
